--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(共通コンポーネント)_(共通コンポーネントID)_(共通コンポーネント名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(共通コンポーネント)_(共通コンポーネントID)_(共通コンポーネント名).xlsx
@@ -9663,8 +9663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -9704,8 +9704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -9739,8 +9739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -9776,8 +9776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -9809,8 +9809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -9842,8 +9842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -9875,8 +9875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -9908,8 +9908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -9945,8 +9945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -9978,8 +9978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -10011,8 +10011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -10046,8 +10046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -10079,8 +10079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -10112,8 +10112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -10145,8 +10145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -10182,8 +10182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -10215,8 +10215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -10252,8 +10252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -10285,8 +10285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -10320,8 +10320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -10353,8 +10353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -10386,8 +10386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -10419,8 +10419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -10454,8 +10454,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -10487,8 +10487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -10522,8 +10522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -10561,8 +10561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -10594,8 +10594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -10627,8 +10627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -10660,8 +10660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -10697,8 +10697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -10730,8 +10730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -10771,8 +10771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -10804,8 +10804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -10837,8 +10837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -10872,8 +10872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -10905,8 +10905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -10938,8 +10938,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -10973,8 +10973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -11006,8 +11006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -11041,8 +11041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -11074,8 +11074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -11107,8 +11107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -11140,8 +11140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -11173,8 +11173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -11206,8 +11206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -11241,8 +11241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -11276,8 +11276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -11311,8 +11311,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -11348,8 +11348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -11381,8 +11381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -11414,8 +11414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -11447,8 +11447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -11480,8 +11480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -11515,8 +11515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -11548,8 +11548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -11581,8 +11581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -11614,8 +11614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -11647,8 +11647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -11680,8 +11680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -11713,8 +11713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -11746,8 +11746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -11781,8 +11781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -11816,8 +11816,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -11849,8 +11849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -11882,8 +11882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -11915,8 +11915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -11948,8 +11948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -11987,8 +11987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -12020,8 +12020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -12055,8 +12055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -12090,8 +12090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -12123,8 +12123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -12158,8 +12158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -12193,8 +12193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -12232,8 +12232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -12267,8 +12267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -12302,8 +12302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -12341,8 +12341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -12374,8 +12374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -12409,8 +12409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -12444,8 +12444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -12477,8 +12477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -12512,8 +12512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -12551,8 +12551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -12584,8 +12584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -12617,8 +12617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -12650,8 +12650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -12683,8 +12683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -12718,8 +12718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -12751,8 +12751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -12784,8 +12784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -12817,8 +12817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -12850,8 +12850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -12885,8 +12885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -12926,8 +12926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -12965,8 +12965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -12998,8 +12998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -13037,8 +13037,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -13076,8 +13076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -13109,8 +13109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -13150,8 +13150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -13185,8 +13185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -13218,8 +13218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -13251,8 +13251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -13286,8 +13286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -13319,8 +13319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -13352,8 +13352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -13385,8 +13385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -13418,8 +13418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -13453,8 +13453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -13486,8 +13486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -13519,8 +13519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -13552,8 +13552,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -13585,8 +13585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -13620,8 +13620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -13657,8 +13657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -13696,8 +13696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -13731,8 +13731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -13764,8 +13764,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -13797,8 +13797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -13838,8 +13838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -13873,8 +13873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -13906,8 +13906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -13939,8 +13939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -13974,8 +13974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -14007,8 +14007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -14044,8 +14044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -14083,8 +14083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -14118,8 +14118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -14153,8 +14153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -14188,8 +14188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -14223,8 +14223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -14258,8 +14258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -14291,8 +14291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -14324,8 +14324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -14357,8 +14357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -14390,8 +14390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -14423,8 +14423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -14460,8 +14460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -14493,8 +14493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -14528,8 +14528,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -14561,8 +14561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -14594,8 +14594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -14627,8 +14627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -14660,8 +14660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -14693,8 +14693,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -14726,8 +14726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -14759,8 +14759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -14792,8 +14792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -14825,8 +14825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -14858,8 +14858,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -14893,8 +14893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -14926,8 +14926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -14959,8 +14959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -14992,8 +14992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -15025,8 +15025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -15058,8 +15058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -15091,8 +15091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -15126,8 +15126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -15159,8 +15159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -15192,8 +15192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -15225,8 +15225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -15258,8 +15258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -15291,8 +15291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -15324,8 +15324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -15357,8 +15357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -15390,8 +15390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -15425,8 +15425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -15460,8 +15460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -15501,8 +15501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -15538,8 +15538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -15575,8 +15575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -15616,8 +15616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -15651,8 +15651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -15684,8 +15684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -15719,8 +15719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -15752,8 +15752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -15789,8 +15789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -15828,8 +15828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -15861,8 +15861,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -15894,8 +15894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -15927,8 +15927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -15960,8 +15960,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -15993,8 +15993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -16026,8 +16026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -16061,8 +16061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -16098,8 +16098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -16131,8 +16131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -16164,8 +16164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -16197,8 +16197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -16230,8 +16230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -16263,8 +16263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -16296,8 +16296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -16329,8 +16329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -16362,8 +16362,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -16395,8 +16395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -16428,8 +16428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -16461,8 +16461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -16494,8 +16494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -16531,8 +16531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -16564,8 +16564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -16597,8 +16597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -16630,8 +16630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -16663,8 +16663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -16696,8 +16696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -16729,8 +16729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -16762,8 +16762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -16795,8 +16795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -16828,8 +16828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -16861,8 +16861,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -16894,8 +16894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -16927,8 +16927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -16960,8 +16960,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -16993,8 +16993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -17028,8 +17028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -17061,8 +17061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -17094,8 +17094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -17129,8 +17129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -17164,8 +17164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -17205,8 +17205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -17240,8 +17240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -17273,8 +17273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -17306,8 +17306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -17339,8 +17339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -17372,8 +17372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -17407,8 +17407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -17440,8 +17440,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -17473,8 +17473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -17506,8 +17506,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -17539,8 +17539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -17574,8 +17574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -17613,8 +17613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -17654,8 +17654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -17687,8 +17687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -17724,8 +17724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -17757,8 +17757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -17796,8 +17796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -17831,8 +17831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -17866,8 +17866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -17901,8 +17901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -17938,8 +17938,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -17971,8 +17971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -18006,8 +18006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -18039,8 +18039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -18072,8 +18072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -18105,8 +18105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -18138,8 +18138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -18171,8 +18171,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -18204,8 +18204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -18237,8 +18237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -18270,8 +18270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -18303,8 +18303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -18336,8 +18336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -18371,8 +18371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -18404,8 +18404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -18437,8 +18437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -18470,8 +18470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -18503,8 +18503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -18536,8 +18536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -18571,8 +18571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -18604,8 +18604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -18637,8 +18637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -18670,8 +18670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -18703,8 +18703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -18736,8 +18736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -18769,8 +18769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -18802,8 +18802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -18837,8 +18837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -18878,8 +18878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -18911,8 +18911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -18944,8 +18944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -18977,8 +18977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -19016,8 +19016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -19051,8 +19051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -19086,8 +19086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -19121,8 +19121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -19158,8 +19158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -19191,8 +19191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -19224,8 +19224,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -19257,8 +19257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -19290,8 +19290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -19323,8 +19323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -19356,8 +19356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -19389,8 +19389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
